--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_02-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_02-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="118">
   <si>
     <t>SKU</t>
   </si>
@@ -365,6 +365,10 @@
   </si>
   <si>
     <t>POA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: Message: 
+</t>
   </si>
 </sst>
 </file>
@@ -816,7 +820,7 @@
         <v>116</v>
       </c>
       <c r="O2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -863,7 +867,7 @@
         <v>116</v>
       </c>
       <c r="O3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -910,7 +914,7 @@
         <v>116</v>
       </c>
       <c r="O4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -957,7 +961,7 @@
         <v>116</v>
       </c>
       <c r="O5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1004,7 +1008,7 @@
         <v>116</v>
       </c>
       <c r="O6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1051,7 +1055,7 @@
         <v>116</v>
       </c>
       <c r="O7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1098,7 +1102,7 @@
         <v>116</v>
       </c>
       <c r="O8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1145,7 +1149,7 @@
         <v>116</v>
       </c>
       <c r="O9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1192,7 +1196,7 @@
         <v>116</v>
       </c>
       <c r="O10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1239,7 +1243,7 @@
         <v>116</v>
       </c>
       <c r="O11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1286,7 +1290,7 @@
         <v>116</v>
       </c>
       <c r="O12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1333,7 +1337,7 @@
         <v>116</v>
       </c>
       <c r="O13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1427,7 +1431,7 @@
         <v>116</v>
       </c>
       <c r="O15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -1474,7 +1478,7 @@
         <v>116</v>
       </c>
       <c r="O16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -1521,7 +1525,7 @@
         <v>116</v>
       </c>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
